--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/05062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/05062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes, 5 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Marcos
-Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
-*Oración de la mañana*
-Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
-Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
-Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
-Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>viernes, 5 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 35-37 Un día, mientras enseñaba en el templo, Jesús preguntó: “¿Cómo pueden decir los escribas que el Mesías es hijo de David? El mismo David, inspirado por el Espíritu Santo, ha declarado: Dijo el Señor a mi Señor: Siéntate a mi derecha y yo haré de tus enemigos el estrado donde pongas los pies. Si el mismo David lo llama ‘Señor’, ¿cómo puede ser hijo suyo?” La multitud que lo rodeaba, que era mucha, lo escuchaba con agrado.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas con palabras llenas de sabiduría, ilumina nuestro entendimiento para comprender el verdadero significado de tus enseñanzas. Ayúdanos a entender que Tú eres más que un descendiente de David, eres el Mesías, el Señor de señores, que trasciendes todas las generaciones y las limitaciones humanas.
+Amado Padre, gracias por este nuevo día que nos regalas, un día para crecer en la fe y acercarnos más a Ti. Ayúdanos a ser humildes, a reconocer que Tú eres el principio y el fin, el creador de todo lo que existe. Que nuestras acciones del día sean un reflejo de tu amor y bondad, y que en todo momento te reconozcamos como nuestro supremo Señor.
+Espíritu Santo, fuente de inspiración, guía nuestros pensamientos y nuestras palabras hoy y siempre. Permítenos ser conductos de tu sabiduría, para que nuestras vidas sean testimonio de tu presencia en el mundo. Ayúdanos a ser valientes y fieles en medio de las adversidades, y a nunca olvidar que Tú eres la fuente de nuestra fuerza y nuestra paz.
+Confiados en tu misericordia y amor, te lo pedimos por Jesucristo nuestro Señor. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>